--- a/test/fixtures/historic_data-cost.xlsx
+++ b/test/fixtures/historic_data-cost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1da6715471b04c19/Energiepad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{784B77AE-666E-4447-B6AE-289E6BD4A9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41F1B52F-1BD1-4624-9CDE-43704EFAE016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="1" xr2:uid="{9C2A921D-B569-4AD4-927C-EE7B618C6C13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{9C2A921D-B569-4AD4-927C-EE7B618C6C13}"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="33">
   <si>
     <t>Year</t>
   </si>
@@ -58,6 +58,9 @@
     <t>GBP</t>
   </si>
   <si>
+    <t>Site Name</t>
+  </si>
+  <si>
     <t>Jan VAT Cost</t>
   </si>
   <si>
@@ -127,13 +130,16 @@
     <t>Dec Total Cost</t>
   </si>
   <si>
-    <t>Site</t>
-  </si>
-  <si>
     <t>Site 604</t>
   </si>
   <si>
+    <t>Main Building A</t>
+  </si>
+  <si>
     <t>site 606</t>
+  </si>
+  <si>
+    <t>Main Building B</t>
   </si>
 </sst>
 </file>
@@ -485,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD0D3C91-81B8-4B2C-9EA6-592D33770954}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
@@ -512,7 +518,7 @@
     <col min="23" max="23" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -520,7 +526,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -528,7 +534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -536,7 +542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -568,7 +574,7 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
         <v>14</v>
@@ -612,177 +618,186 @@
       <c r="Y4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>51</v>
+      </c>
+      <c r="E5">
+        <v>56</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>416</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>52</v>
+      </c>
+      <c r="K5">
+        <v>515</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>56</v>
+      </c>
+      <c r="N5">
+        <v>2</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>5</v>
+      </c>
+      <c r="Q5">
+        <v>32</v>
+      </c>
+      <c r="R5">
+        <v>43</v>
+      </c>
+      <c r="S5">
+        <v>4</v>
+      </c>
+      <c r="T5">
+        <v>5</v>
+      </c>
+      <c r="U5">
+        <v>8</v>
+      </c>
+      <c r="V5">
+        <v>4</v>
+      </c>
+      <c r="W5">
+        <v>52</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>5</v>
+      </c>
+      <c r="Z5">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>25</v>
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>12</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
         <v>51</v>
       </c>
-      <c r="D6">
-        <v>56</v>
-      </c>
-      <c r="E6">
-        <v>8</v>
-      </c>
-      <c r="F6">
-        <v>416</v>
-      </c>
       <c r="G6">
         <v>5</v>
       </c>
       <c r="H6">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I6">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="J6">
-        <v>515</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="M6">
+        <v>12</v>
+      </c>
+      <c r="N6">
+        <v>23</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <v>54</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
+      <c r="S6">
+        <v>12</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
         <v>2</v>
       </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>5</v>
-      </c>
-      <c r="P6">
-        <v>32</v>
-      </c>
-      <c r="Q6">
-        <v>43</v>
-      </c>
-      <c r="R6">
-        <v>4</v>
-      </c>
-      <c r="S6">
-        <v>5</v>
-      </c>
-      <c r="T6">
-        <v>8</v>
-      </c>
-      <c r="U6">
-        <v>4</v>
-      </c>
       <c r="V6">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="W6">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>12</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>51</v>
-      </c>
-      <c r="F7">
-        <v>5</v>
-      </c>
-      <c r="G7">
-        <v>12</v>
-      </c>
-      <c r="H7">
-        <v>13</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>12</v>
-      </c>
-      <c r="M7">
-        <v>23</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>5</v>
-      </c>
-      <c r="P7">
-        <v>54</v>
-      </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="R7">
-        <v>12</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>2</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7">
-        <v>51</v>
-      </c>
-      <c r="W7">
-        <v>2</v>
-      </c>
-      <c r="X7">
-        <v>1</v>
-      </c>
-      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z6">
         <v>21</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{A3730472-004F-470D-919E-EE4C02E1ED40}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCDA408F-A894-4B90-8E8C-D85E971625A1}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -790,7 +805,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -798,7 +813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -806,7 +821,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -838,7 +853,7 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
         <v>14</v>
@@ -882,177 +897,186 @@
       <c r="Y4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>645</v>
+      </c>
+      <c r="D5">
+        <v>6121</v>
+      </c>
+      <c r="E5">
+        <v>81</v>
+      </c>
+      <c r="F5">
+        <v>951</v>
+      </c>
+      <c r="G5">
+        <v>51</v>
+      </c>
+      <c r="H5">
+        <v>31</v>
+      </c>
+      <c r="I5">
+        <v>515</v>
+      </c>
+      <c r="J5">
+        <v>15</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>15</v>
+      </c>
+      <c r="M5">
+        <v>16</v>
+      </c>
+      <c r="N5">
+        <v>8</v>
+      </c>
+      <c r="O5">
+        <v>48</v>
+      </c>
+      <c r="P5">
+        <v>46</v>
+      </c>
+      <c r="Q5">
+        <v>32</v>
+      </c>
+      <c r="R5">
+        <v>43</v>
+      </c>
+      <c r="S5">
+        <v>54</v>
+      </c>
+      <c r="T5">
+        <v>9</v>
+      </c>
+      <c r="U5">
+        <v>854</v>
+      </c>
+      <c r="V5">
+        <v>21</v>
+      </c>
+      <c r="W5">
+        <v>65</v>
+      </c>
+      <c r="X5">
+        <v>4</v>
+      </c>
+      <c r="Y5">
+        <v>84</v>
+      </c>
+      <c r="Z5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>645</v>
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
-        <v>6121</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="E6">
-        <v>951</v>
+        <v>32</v>
       </c>
       <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>516</v>
+      </c>
+      <c r="H6">
         <v>51</v>
       </c>
-      <c r="G6">
-        <v>31</v>
-      </c>
-      <c r="H6">
-        <v>515</v>
-      </c>
       <c r="I6">
-        <v>15</v>
+        <v>654</v>
       </c>
       <c r="J6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L6">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="M6">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="N6">
-        <v>48</v>
+        <v>654</v>
       </c>
       <c r="O6">
-        <v>46</v>
+        <v>984</v>
       </c>
       <c r="P6">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="Q6">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="R6">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="T6">
-        <v>854</v>
+        <v>4</v>
       </c>
       <c r="U6">
-        <v>21</v>
+        <v>541</v>
       </c>
       <c r="V6">
-        <v>65</v>
+        <v>651</v>
       </c>
       <c r="W6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X6">
-        <v>84</v>
+        <v>1651</v>
       </c>
       <c r="Y6">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>21</v>
-      </c>
-      <c r="C7">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>516</v>
-      </c>
-      <c r="G7">
-        <v>51</v>
-      </c>
-      <c r="H7">
-        <v>654</v>
-      </c>
-      <c r="I7">
-        <v>5</v>
-      </c>
-      <c r="J7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>49</v>
-      </c>
-      <c r="L7">
-        <v>84</v>
-      </c>
-      <c r="M7">
-        <v>654</v>
-      </c>
-      <c r="N7">
-        <v>984</v>
-      </c>
-      <c r="O7">
-        <v>5</v>
-      </c>
-      <c r="P7">
-        <v>54</v>
-      </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="R7">
-        <v>49</v>
-      </c>
-      <c r="S7">
-        <v>4</v>
-      </c>
-      <c r="T7">
-        <v>541</v>
-      </c>
-      <c r="U7">
-        <v>651</v>
-      </c>
-      <c r="V7">
-        <v>5</v>
-      </c>
-      <c r="W7">
-        <v>1651</v>
-      </c>
-      <c r="X7">
-        <v>5</v>
-      </c>
-      <c r="Y7">
+        <v>5</v>
+      </c>
+      <c r="Z6">
         <v>154</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{2815D562-B321-4150-BC07-6FD1CD76DDDE}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C019B3D-5E46-4EA1-B2CD-391AB69703C6}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1084,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1068,7 +1092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1076,7 +1100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1108,7 +1132,7 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
         <v>14</v>
@@ -1152,177 +1176,186 @@
       <c r="Y4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>35</v>
+      </c>
+      <c r="E5">
+        <v>496</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>45</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>21</v>
+      </c>
+      <c r="J5">
+        <v>51</v>
+      </c>
+      <c r="K5">
+        <v>54</v>
+      </c>
+      <c r="L5">
+        <v>5</v>
+      </c>
+      <c r="M5">
+        <v>48</v>
+      </c>
+      <c r="N5">
+        <v>48</v>
+      </c>
+      <c r="O5">
+        <v>49</v>
+      </c>
+      <c r="P5">
+        <v>6</v>
+      </c>
+      <c r="Q5">
+        <v>32</v>
+      </c>
+      <c r="R5">
+        <v>43</v>
+      </c>
+      <c r="S5">
+        <v>32</v>
+      </c>
+      <c r="T5">
+        <v>13</v>
+      </c>
+      <c r="U5">
+        <v>74</v>
+      </c>
+      <c r="V5">
+        <v>9</v>
+      </c>
+      <c r="W5">
+        <v>87</v>
+      </c>
+      <c r="X5">
+        <v>95</v>
+      </c>
+      <c r="Y5">
+        <v>84</v>
+      </c>
+      <c r="Z5">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>6</v>
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D6">
-        <v>496</v>
+        <v>695</v>
       </c>
       <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>141</v>
+      </c>
+      <c r="G6">
+        <v>98</v>
+      </c>
+      <c r="H6">
+        <v>48</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <v>984</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6">
+        <v>489</v>
+      </c>
+      <c r="M6">
         <v>8</v>
       </c>
-      <c r="F6">
+      <c r="N6">
         <v>45</v>
       </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>21</v>
-      </c>
-      <c r="I6">
-        <v>51</v>
-      </c>
-      <c r="J6">
+      <c r="O6">
+        <v>462</v>
+      </c>
+      <c r="P6">
+        <v>16</v>
+      </c>
+      <c r="Q6">
         <v>54</v>
       </c>
-      <c r="K6">
-        <v>5</v>
-      </c>
-      <c r="L6">
-        <v>48</v>
-      </c>
-      <c r="M6">
-        <v>48</v>
-      </c>
-      <c r="N6">
-        <v>49</v>
-      </c>
-      <c r="O6">
-        <v>6</v>
-      </c>
-      <c r="P6">
-        <v>32</v>
-      </c>
-      <c r="Q6">
-        <v>43</v>
-      </c>
       <c r="R6">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="S6">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="U6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="V6">
-        <v>87</v>
+        <v>34</v>
       </c>
       <c r="W6">
-        <v>95</v>
+        <v>464</v>
       </c>
       <c r="X6">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="Y6">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>54</v>
-      </c>
-      <c r="C7">
-        <v>695</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>141</v>
-      </c>
-      <c r="F7">
-        <v>98</v>
-      </c>
-      <c r="G7">
-        <v>48</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>984</v>
-      </c>
-      <c r="J7">
-        <v>9</v>
-      </c>
-      <c r="K7">
-        <v>489</v>
-      </c>
-      <c r="L7">
-        <v>8</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
-      </c>
-      <c r="N7">
-        <v>462</v>
-      </c>
-      <c r="O7">
-        <v>16</v>
-      </c>
-      <c r="P7">
-        <v>54</v>
-      </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="R7">
-        <v>5</v>
-      </c>
-      <c r="S7">
-        <v>46</v>
-      </c>
-      <c r="T7">
-        <v>4</v>
-      </c>
-      <c r="U7">
-        <v>34</v>
-      </c>
-      <c r="V7">
-        <v>464</v>
-      </c>
-      <c r="W7">
         <v>94</v>
       </c>
-      <c r="X7">
-        <v>94</v>
-      </c>
-      <c r="Y7">
+      <c r="Z6">
         <v>944</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{9481A47F-055E-4932-972F-44C9FE900542}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30860D19-32F8-43EA-92B0-7FBF06963904}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1330,7 +1363,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1338,7 +1371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1346,7 +1379,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1378,7 +1411,7 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
         <v>14</v>
@@ -1422,177 +1455,186 @@
       <c r="Y4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>696</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>21</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>84</v>
+      </c>
+      <c r="I5">
+        <v>54</v>
+      </c>
+      <c r="J5">
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>31</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>19</v>
+      </c>
+      <c r="O5">
+        <v>854</v>
+      </c>
+      <c r="P5">
+        <v>984</v>
+      </c>
+      <c r="Q5">
+        <v>32</v>
+      </c>
+      <c r="R5">
+        <v>43</v>
+      </c>
+      <c r="S5">
+        <v>65</v>
+      </c>
+      <c r="T5">
+        <v>46</v>
+      </c>
+      <c r="U5">
+        <v>51</v>
+      </c>
+      <c r="V5">
+        <v>51</v>
+      </c>
+      <c r="W5">
+        <v>65</v>
+      </c>
+      <c r="X5">
+        <v>15</v>
+      </c>
+      <c r="Y5">
+        <v>51</v>
+      </c>
+      <c r="Z5">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>696</v>
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>478</v>
+      </c>
+      <c r="I6">
         <v>4</v>
       </c>
-      <c r="D6">
-        <v>21</v>
-      </c>
-      <c r="E6">
+      <c r="J6">
+        <v>87</v>
+      </c>
+      <c r="K6">
+        <v>8</v>
+      </c>
+      <c r="L6">
+        <v>9</v>
+      </c>
+      <c r="M6">
+        <v>6</v>
+      </c>
+      <c r="N6">
+        <v>33</v>
+      </c>
+      <c r="O6">
+        <v>6</v>
+      </c>
+      <c r="P6">
+        <v>6</v>
+      </c>
+      <c r="Q6">
+        <v>54</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
+      <c r="S6">
+        <v>65</v>
+      </c>
+      <c r="T6">
         <v>4</v>
       </c>
-      <c r="F6">
-        <v>84</v>
-      </c>
-      <c r="G6">
-        <v>84</v>
-      </c>
-      <c r="H6">
-        <v>54</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>31</v>
-      </c>
-      <c r="L6">
-        <v>5</v>
-      </c>
-      <c r="M6">
-        <v>19</v>
-      </c>
-      <c r="N6">
-        <v>854</v>
-      </c>
-      <c r="O6">
-        <v>984</v>
-      </c>
-      <c r="P6">
-        <v>32</v>
-      </c>
-      <c r="Q6">
-        <v>43</v>
-      </c>
-      <c r="R6">
-        <v>65</v>
-      </c>
-      <c r="S6">
-        <v>46</v>
-      </c>
-      <c r="T6">
-        <v>51</v>
-      </c>
       <c r="U6">
-        <v>51</v>
+        <v>8</v>
       </c>
       <c r="V6">
-        <v>65</v>
+        <v>1</v>
       </c>
       <c r="W6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="Y6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>16</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>8</v>
-      </c>
-      <c r="G7">
-        <v>478</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="I7">
-        <v>87</v>
-      </c>
-      <c r="J7">
-        <v>8</v>
-      </c>
-      <c r="K7">
-        <v>9</v>
-      </c>
-      <c r="L7">
-        <v>6</v>
-      </c>
-      <c r="M7">
-        <v>33</v>
-      </c>
-      <c r="N7">
-        <v>6</v>
-      </c>
-      <c r="O7">
-        <v>6</v>
-      </c>
-      <c r="P7">
-        <v>54</v>
-      </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="R7">
-        <v>65</v>
-      </c>
-      <c r="S7">
-        <v>4</v>
-      </c>
-      <c r="T7">
-        <v>8</v>
-      </c>
-      <c r="U7">
-        <v>1</v>
-      </c>
-      <c r="V7">
-        <v>8</v>
-      </c>
-      <c r="W7">
         <v>48</v>
       </c>
-      <c r="X7">
+      <c r="Z6">
         <v>48</v>
       </c>
-      <c r="Y7">
-        <v>48</v>
-      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{C323160F-EE40-493C-B829-894DD1CD1E79}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88C0E0B6-D385-4078-85E9-5FAD623C534C}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1600,7 +1642,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1608,7 +1650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1616,7 +1658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1648,7 +1690,7 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
         <v>14</v>
@@ -1692,181 +1734,190 @@
       <c r="Y4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>14</v>
+      </c>
+      <c r="D5">
+        <v>544</v>
+      </c>
+      <c r="E5">
+        <v>121</v>
+      </c>
+      <c r="F5">
+        <v>6</v>
+      </c>
+      <c r="G5">
+        <v>16</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>213</v>
+      </c>
+      <c r="J5">
+        <v>5</v>
+      </c>
+      <c r="K5">
+        <v>15</v>
+      </c>
+      <c r="L5">
+        <v>15</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>9</v>
+      </c>
+      <c r="O5">
+        <v>84</v>
+      </c>
+      <c r="P5">
+        <v>84</v>
+      </c>
+      <c r="Q5">
+        <v>32</v>
+      </c>
+      <c r="R5">
+        <v>43</v>
+      </c>
+      <c r="S5">
+        <v>84</v>
+      </c>
+      <c r="T5">
+        <v>8</v>
+      </c>
+      <c r="U5">
+        <v>5</v>
+      </c>
+      <c r="V5">
+        <v>45</v>
+      </c>
+      <c r="W5">
+        <v>21</v>
+      </c>
+      <c r="X5">
+        <v>5</v>
+      </c>
+      <c r="Y5">
+        <v>45</v>
+      </c>
+      <c r="Z5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>14</v>
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
-        <v>544</v>
+        <v>21</v>
       </c>
       <c r="D6">
-        <v>121</v>
+        <v>65</v>
       </c>
       <c r="E6">
+        <v>15</v>
+      </c>
+      <c r="F6">
+        <v>48</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6">
+        <v>84</v>
+      </c>
+      <c r="I6">
+        <v>9</v>
+      </c>
+      <c r="J6">
+        <v>84</v>
+      </c>
+      <c r="K6">
         <v>6</v>
       </c>
-      <c r="F6">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <v>213</v>
-      </c>
-      <c r="I6">
-        <v>5</v>
-      </c>
-      <c r="J6">
-        <v>15</v>
-      </c>
-      <c r="K6">
-        <v>15</v>
-      </c>
       <c r="L6">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N6">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="O6">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <v>54</v>
+      </c>
+      <c r="R6">
+        <v>5</v>
+      </c>
+      <c r="S6">
+        <v>484</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
+      </c>
+      <c r="U6">
+        <v>65</v>
+      </c>
+      <c r="V6">
         <v>32</v>
       </c>
-      <c r="Q6">
-        <v>43</v>
-      </c>
-      <c r="R6">
-        <v>84</v>
-      </c>
-      <c r="S6">
-        <v>8</v>
-      </c>
-      <c r="T6">
-        <v>5</v>
-      </c>
-      <c r="U6">
+      <c r="W6">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>3</v>
+      </c>
+      <c r="Y6">
         <v>45</v>
       </c>
-      <c r="V6">
-        <v>21</v>
-      </c>
-      <c r="W6">
-        <v>5</v>
-      </c>
-      <c r="X6">
+      <c r="Z6">
         <v>45</v>
       </c>
-      <c r="Y6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>21</v>
-      </c>
-      <c r="C7">
-        <v>65</v>
-      </c>
-      <c r="D7">
-        <v>15</v>
-      </c>
-      <c r="E7">
-        <v>48</v>
-      </c>
-      <c r="F7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>84</v>
-      </c>
-      <c r="H7">
-        <v>9</v>
-      </c>
-      <c r="I7">
-        <v>84</v>
-      </c>
-      <c r="J7">
-        <v>6</v>
-      </c>
-      <c r="K7">
-        <v>8</v>
-      </c>
-      <c r="L7">
-        <v>7</v>
-      </c>
-      <c r="M7">
-        <v>48</v>
-      </c>
-      <c r="N7">
-        <v>54</v>
-      </c>
-      <c r="O7">
-        <v>5</v>
-      </c>
-      <c r="P7">
-        <v>54</v>
-      </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="R7">
-        <v>484</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
-      </c>
-      <c r="T7">
-        <v>65</v>
-      </c>
-      <c r="U7">
-        <v>32</v>
-      </c>
-      <c r="V7">
-        <v>1</v>
-      </c>
-      <c r="W7">
-        <v>3</v>
-      </c>
-      <c r="X7">
-        <v>45</v>
-      </c>
-      <c r="Y7">
-        <v>45</v>
-      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{3C546C6C-11A8-4B04-BC7F-64C807B252BF}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68FA3C0D-D4F0-4CD3-9F83-3519253E74C4}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="15" max="15" width="14.28515625" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25">
+    <row r="1" spans="1:26">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1874,7 +1925,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="2" spans="1:25">
+    <row r="2" spans="1:26">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1882,7 +1933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:26">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1890,7 +1941,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:26">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -1922,7 +1973,7 @@
         <v>13</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L4" t="s">
         <v>14</v>
@@ -1966,167 +2017,176 @@
       <c r="Y4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="5" spans="1:25">
+      <c r="Z4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:25">
+        <v>29</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5">
+        <v>147</v>
+      </c>
+      <c r="D5">
+        <v>21</v>
+      </c>
+      <c r="E5">
+        <v>84</v>
+      </c>
+      <c r="F5">
+        <v>849</v>
+      </c>
+      <c r="G5">
+        <v>84</v>
+      </c>
+      <c r="H5">
+        <v>65</v>
+      </c>
+      <c r="I5">
+        <v>4615</v>
+      </c>
+      <c r="J5">
+        <v>6</v>
+      </c>
+      <c r="K5">
+        <v>54</v>
+      </c>
+      <c r="L5">
+        <v>654</v>
+      </c>
+      <c r="M5">
+        <v>8</v>
+      </c>
+      <c r="N5">
+        <v>745</v>
+      </c>
+      <c r="O5">
+        <v>43</v>
+      </c>
+      <c r="P5">
+        <v>21</v>
+      </c>
+      <c r="Q5">
+        <v>32</v>
+      </c>
+      <c r="R5">
+        <v>43</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>16</v>
+      </c>
+      <c r="U5">
+        <v>54</v>
+      </c>
+      <c r="V5">
+        <v>654</v>
+      </c>
+      <c r="W5">
+        <v>84</v>
+      </c>
+      <c r="X5">
+        <v>84</v>
+      </c>
+      <c r="Y5">
+        <v>321</v>
+      </c>
+      <c r="Z5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6">
-        <v>147</v>
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
       </c>
       <c r="C6">
+        <v>151</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
         <v>21</v>
       </c>
-      <c r="D6">
-        <v>84</v>
-      </c>
-      <c r="E6">
-        <v>849</v>
-      </c>
       <c r="F6">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="G6">
+        <v>48</v>
+      </c>
+      <c r="H6">
+        <v>351</v>
+      </c>
+      <c r="I6">
         <v>65</v>
       </c>
-      <c r="H6">
-        <v>4615</v>
-      </c>
-      <c r="I6">
-        <v>6</v>
-      </c>
       <c r="J6">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K6">
         <v>654</v>
       </c>
       <c r="L6">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M6">
-        <v>745</v>
+        <v>848</v>
       </c>
       <c r="N6">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O6">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="Q6">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="R6">
         <v>5</v>
       </c>
       <c r="S6">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="T6">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="U6">
-        <v>654</v>
+        <v>44</v>
       </c>
       <c r="V6">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="W6">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="X6">
-        <v>321</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:25">
-      <c r="A7" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7">
-        <v>151</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-      <c r="D7">
-        <v>21</v>
-      </c>
-      <c r="E7">
-        <v>35</v>
-      </c>
-      <c r="F7">
-        <v>48</v>
-      </c>
-      <c r="G7">
-        <v>351</v>
-      </c>
-      <c r="H7">
-        <v>65</v>
-      </c>
-      <c r="I7">
-        <v>58</v>
-      </c>
-      <c r="J7">
-        <v>654</v>
-      </c>
-      <c r="K7">
-        <v>2</v>
-      </c>
-      <c r="L7">
-        <v>848</v>
-      </c>
-      <c r="M7">
-        <v>45</v>
-      </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-      <c r="O7">
         <v>51</v>
       </c>
-      <c r="P7">
-        <v>54</v>
-      </c>
-      <c r="Q7">
-        <v>5</v>
-      </c>
-      <c r="R7">
-        <v>48</v>
-      </c>
-      <c r="S7">
-        <v>12</v>
-      </c>
-      <c r="T7">
-        <v>44</v>
-      </c>
-      <c r="U7">
-        <v>5</v>
-      </c>
-      <c r="V7">
-        <v>15</v>
-      </c>
-      <c r="W7">
-        <v>1</v>
-      </c>
-      <c r="X7">
+      <c r="Z6">
         <v>51</v>
       </c>
-      <c r="Y7">
-        <v>51</v>
-      </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{A2BF89E8-4D6E-42B7-9269-8E11E9237560}">
+      <formula1>"Grid Electricity,Gas,Solar PV,Petrol,Diesel,Bio Diesel"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test/fixtures/historic_data-cost.xlsx
+++ b/test/fixtures/historic_data-cost.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1da6715471b04c19/Energiepad/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41F1B52F-1BD1-4624-9CDE-43704EFAE016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAF1388B-F860-4C59-974E-3E11A298A4F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{9C2A921D-B569-4AD4-927C-EE7B618C6C13}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="5" xr2:uid="{9C2A921D-B569-4AD4-927C-EE7B618C6C13}"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="1" r:id="rId1"/>
@@ -1482,7 +1482,7 @@
         <v>84</v>
       </c>
       <c r="H5">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="I5">
         <v>54</v>
@@ -1913,6 +1913,7 @@
   <dimension ref="A1:Z6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
     <col min="15" max="15" width="14.28515625" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
   </cols>
